--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,8 +793,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134664981</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,9 +799,1128 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135896115</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>496245</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6623041</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135896115</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135896164</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>496265</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6623077</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135896164</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135896209</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>496293</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6623075</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135896209</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135896426</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>496321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6623080</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135896426</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135896489</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496422</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6622992</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135896489</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135897036</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496343</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6623118</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troligtvis spelspillning</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135897036</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135897062</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496332</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6623095</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135897062</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135897085</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496282</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6623056</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135897085</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135793017</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hyttskogshöjden, Hyttskogshöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496496</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6623197</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Noterad flera gånger under dagen, spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135793017</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135793153</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hyttskogshöjden, Hyttskogshöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496496</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6623197</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135793153</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135896115</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>135896164</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135896209</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>135896426</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135896489</v>
       </c>
       <c r="B7" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135897036</v>
       </c>
       <c r="B8" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135897062</v>
       </c>
       <c r="B9" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135897085</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135793017</v>
       </c>
       <c r="B11" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>135793153</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135896115</v>
       </c>
       <c r="B3" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>135896164</v>
       </c>
       <c r="B4" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135896209</v>
       </c>
       <c r="B5" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>135896426</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135896489</v>
       </c>
       <c r="B7" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135897036</v>
       </c>
       <c r="B8" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135897062</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135897085</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135793017</v>
       </c>
       <c r="B11" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>135793153</v>
       </c>
       <c r="B12" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135896115</v>
       </c>
       <c r="B3" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>135896164</v>
       </c>
       <c r="B4" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135896209</v>
       </c>
       <c r="B5" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>135896426</v>
       </c>
       <c r="B6" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135896489</v>
       </c>
       <c r="B7" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135897036</v>
       </c>
       <c r="B8" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135897062</v>
       </c>
       <c r="B9" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135897085</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135793017</v>
       </c>
       <c r="B11" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>135793153</v>
       </c>
       <c r="B12" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135896115</v>
       </c>
       <c r="B3" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>135896164</v>
       </c>
       <c r="B4" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135896209</v>
       </c>
       <c r="B5" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>135896426</v>
       </c>
       <c r="B6" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135896489</v>
       </c>
       <c r="B7" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135897036</v>
       </c>
       <c r="B8" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135897062</v>
       </c>
       <c r="B9" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135897085</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135793017</v>
       </c>
       <c r="B11" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>135793153</v>
       </c>
       <c r="B12" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135896115</v>
       </c>
       <c r="B3" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>135896164</v>
       </c>
       <c r="B4" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135896209</v>
       </c>
       <c r="B5" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>135896426</v>
       </c>
       <c r="B6" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135896489</v>
       </c>
       <c r="B7" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135897036</v>
       </c>
       <c r="B8" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135897062</v>
       </c>
       <c r="B9" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135897085</v>
       </c>
       <c r="B10" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135793017</v>
       </c>
       <c r="B11" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>135793153</v>
       </c>
       <c r="B12" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29404-2026 artfynd.xlsx
+++ b/artfynd/A 29404-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135896115</v>
       </c>
       <c r="B3" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>135896164</v>
       </c>
       <c r="B4" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135896209</v>
       </c>
       <c r="B5" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>135896426</v>
       </c>
       <c r="B6" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135896489</v>
       </c>
       <c r="B7" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>135897036</v>
       </c>
       <c r="B8" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135897062</v>
       </c>
       <c r="B9" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135897085</v>
       </c>
       <c r="B10" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
